--- a/Hardware/mini-vehiculo-exploracion-pcb/Assets/componentes.xlsx
+++ b/Hardware/mini-vehiculo-exploracion-pcb/Assets/componentes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\STAY AWAY MUGGLE\FIUNA\Proyecto 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\STAY AWAY MUGGLE\FIUNA\mini-vehiculo-exploracion\Hardware\mini-vehiculo-exploracion-pcb\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D81EE84-ED7C-48E3-9B78-1FE8791F224F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036B1AAB-E9E8-4BFB-8A15-322A6F99797B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FD0E3963-897E-470D-880E-FBDA975F4A9A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
   <si>
     <t>Ítem</t>
   </si>
@@ -84,9 +84,6 @@
     <t>Cámara OV2640</t>
   </si>
   <si>
-    <t>https://a.co/d/020tRLTxMega2560-Raspberry/dp/B012UXNDOY</t>
-  </si>
-  <si>
     <t>Driver DRV8873HPWPRQ1</t>
   </si>
   <si>
@@ -181,6 +178,60 @@
   </si>
   <si>
     <t>0ppm 1/20W</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0fQ19Ojj</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4sGNgPo</t>
+  </si>
+  <si>
+    <t>USB Receptacle</t>
+  </si>
+  <si>
+    <t>Diodo de Protección ESD / Diodo TVS</t>
+  </si>
+  <si>
+    <t>https://mou.sr/3QKlXSP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fusible </t>
+  </si>
+  <si>
+    <t>https://mou.sr/3NeqxLN</t>
+  </si>
+  <si>
+    <t>Diodo Schottky y Rectificador</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4sOo1Ls</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4qtT9xZ</t>
+  </si>
+  <si>
+    <t>5% 50V</t>
+  </si>
+  <si>
+    <t>https://mou.sr/3NDR59j</t>
+  </si>
+  <si>
+    <t>Resistencia 5.1 kOhm</t>
+  </si>
+  <si>
+    <t>0.1% 25ppm 1/10W</t>
+  </si>
+  <si>
+    <t>https://mou.sr/3Nd8K7H</t>
+  </si>
+  <si>
+    <t>Diodo de Protección ESD</t>
+  </si>
+  <si>
+    <t>https://mou.sr/3JC1Jeg</t>
+  </si>
+  <si>
+    <t>Cristal 32.7680 kHz</t>
   </si>
 </sst>
 </file>
@@ -296,7 +347,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -317,6 +368,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -633,13 +686,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5052AD-E57D-4C3D-BF60-E11D66D6B798}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.44140625" customWidth="1"/>
     <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -663,7 +716,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -732,7 +785,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <f t="shared" ref="A5:A22" si="0">1+A4</f>
+        <f t="shared" ref="A5:A30" si="0">1+A4</f>
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -746,7 +799,7 @@
         <v>56649.5</v>
       </c>
       <c r="E5" s="5">
-        <f t="shared" ref="E5:E22" si="1">+D5*C5</f>
+        <f t="shared" ref="E5:E30" si="1">+D5*C5</f>
         <v>56649.5</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -774,11 +827,11 @@
         <v>178031.5</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="G6" s="7"/>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J6" s="8"/>
     </row>
@@ -788,7 +841,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2">
         <v>2</v>
@@ -802,11 +855,11 @@
         <v>54389</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7" s="7"/>
       <c r="I7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J7" s="9"/>
     </row>
@@ -816,7 +869,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2">
         <v>4</v>
@@ -830,13 +883,13 @@
         <v>5480</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J8" s="10"/>
     </row>
@@ -846,7 +899,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -860,13 +913,13 @@
         <v>685</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J9" s="14"/>
     </row>
@@ -876,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2">
         <v>5</v>
@@ -890,10 +943,10 @@
         <v>4452.5</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -902,7 +955,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
@@ -916,10 +969,10 @@
         <v>1644</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -928,7 +981,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
@@ -942,10 +995,10 @@
         <v>1370</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -954,7 +1007,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
@@ -968,7 +1021,7 @@
         <v>27536.999999999996</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" s="7"/>
     </row>
@@ -978,7 +1031,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -992,7 +1045,7 @@
         <v>1233</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G14" s="7"/>
     </row>
@@ -1002,7 +1055,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="2">
         <v>4</v>
@@ -1016,10 +1069,10 @@
         <v>16714</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1028,7 +1081,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
@@ -1042,10 +1095,10 @@
         <v>1507</v>
       </c>
       <c r="F16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1054,7 +1107,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -1068,13 +1121,13 @@
         <v>685</v>
       </c>
       <c r="F17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="I17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1082,14 +1135,23 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="5"/>
+      <c r="B18" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5">
+        <f>0.53*J3</f>
+        <v>3630.5</v>
+      </c>
       <c r="E18" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="4"/>
+        <v>3630.5</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1097,14 +1159,23 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="5"/>
+      <c r="B19" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5">
+        <f>0.36*J3</f>
+        <v>2466</v>
+      </c>
       <c r="E19" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="4"/>
+        <v>2466</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1112,14 +1183,23 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="5"/>
+      <c r="B20" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5">
+        <f>0.31*J3</f>
+        <v>2123.5</v>
+      </c>
       <c r="E20" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="4"/>
+        <v>2123.5</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1127,14 +1207,23 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="5"/>
+      <c r="B21" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
+        <f>0.35*J3</f>
+        <v>2397.5</v>
+      </c>
       <c r="E21" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="2"/>
+        <v>2397.5</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1142,15 +1231,175 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="5"/>
+      <c r="B22" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
+        <f>0.2*J3</f>
+        <v>1370</v>
+      </c>
       <c r="E22" s="5">
         <f t="shared" si="1"/>
+        <v>1370</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5">
+        <f>0.22*J3</f>
+        <v>1507</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="1"/>
+        <v>3014</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5">
+        <f>0.43*J3</f>
+        <v>2945.5</v>
+      </c>
+      <c r="E24" s="5">
+        <f t="shared" si="1"/>
+        <v>2945.5</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5">
+        <f>0.58*J3</f>
+        <v>3972.9999999999995</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" si="1"/>
+        <v>3972.9999999999995</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="7"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1169,8 +1418,16 @@
     <hyperlink ref="F15" r:id="rId13" xr:uid="{CB98356C-D2C9-46B4-9472-35C102687020}"/>
     <hyperlink ref="F16" r:id="rId14" xr:uid="{0E83BAD7-E761-4479-827D-EFCD9C540B64}"/>
     <hyperlink ref="F17" r:id="rId15" xr:uid="{5832DA8D-1D91-4BA2-A2D4-66ADE83D90AC}"/>
+    <hyperlink ref="F18" r:id="rId16" xr:uid="{771AA51C-6524-4515-B611-123D4125843F}"/>
+    <hyperlink ref="F19" r:id="rId17" xr:uid="{0E3B9535-05EC-41BD-AEA4-2A7FFEA4202F}"/>
+    <hyperlink ref="F20" r:id="rId18" xr:uid="{D7482E33-5741-4772-BE1F-1C86D70BBB69}"/>
+    <hyperlink ref="F21" r:id="rId19" xr:uid="{DCF11D56-D35C-4F46-928E-D4EEFCC2D5C3}"/>
+    <hyperlink ref="F22" r:id="rId20" xr:uid="{CCDC8CEA-D755-4010-A535-AC6796494C79}"/>
+    <hyperlink ref="F23" r:id="rId21" xr:uid="{0E642852-5587-4BB4-9B46-453C26D50C0A}"/>
+    <hyperlink ref="F24" r:id="rId22" xr:uid="{CFC35A0D-235D-4F0F-ACB1-2308605BCF6D}"/>
+    <hyperlink ref="F25" r:id="rId23" xr:uid="{6D01D0F5-F729-4C23-954F-F4F0335975FC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId16"/>
+  <pageSetup orientation="portrait" r:id="rId24"/>
 </worksheet>
 </file>
--- a/Hardware/mini-vehiculo-exploracion-pcb/Assets/componentes.xlsx
+++ b/Hardware/mini-vehiculo-exploracion-pcb/Assets/componentes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\STAY AWAY MUGGLE\FIUNA\mini-vehiculo-exploracion\Hardware\mini-vehiculo-exploracion-pcb\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036B1AAB-E9E8-4BFB-8A15-322A6F99797B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EEF678-D41A-4861-BBF8-1AC39AB31E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FD0E3963-897E-470D-880E-FBDA975F4A9A}"/>
   </bookViews>
@@ -734,22 +734,22 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>7</v>
+      <c r="B3" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <f>6.23*J3</f>
-        <v>42675.5</v>
+        <f>13.4*J3</f>
+        <v>91790</v>
       </c>
       <c r="E3" s="5">
         <f>+D3*C3</f>
-        <v>42675.5</v>
+        <v>91790</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G3" s="7"/>
       <c r="I3" t="s">
@@ -765,21 +765,21 @@
         <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="5">
-        <f>13.4*J3</f>
-        <v>91790</v>
+        <f>8.27*J3</f>
+        <v>56649.5</v>
       </c>
       <c r="E4" s="5">
         <f>+D4*C4</f>
-        <v>91790</v>
+        <v>56649.5</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4" s="7"/>
     </row>
@@ -789,47 +789,51 @@
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" s="5">
-        <f>8.27*J3</f>
-        <v>56649.5</v>
+        <f>0.2*J3</f>
+        <v>1370</v>
       </c>
       <c r="E5" s="5">
-        <f t="shared" ref="E5:E30" si="1">+D5*C5</f>
-        <v>56649.5</v>
+        <f>+D5*C5</f>
+        <v>5480</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="7"/>
+        <v>23</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>14</v>
+      <c r="B6" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="5">
-        <f>25.99*J3</f>
-        <v>178031.5</v>
+        <f>0.1*J3</f>
+        <v>685</v>
       </c>
       <c r="E6" s="5">
-        <f t="shared" si="1"/>
-        <v>178031.5</v>
+        <f>+D6*C6</f>
+        <v>685</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="7"/>
+        <v>26</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="I6" t="s">
         <v>33</v>
       </c>
@@ -840,24 +844,26 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>15</v>
+      <c r="B7" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" s="5">
-        <f>3.97*J3</f>
-        <v>27194.5</v>
+        <f>0.13*J3</f>
+        <v>890.5</v>
       </c>
       <c r="E7" s="5">
-        <f t="shared" si="1"/>
-        <v>54389</v>
+        <f>+D7*C7</f>
+        <v>4452.5</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="7"/>
+        <v>28</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="I7" t="s">
         <v>34</v>
       </c>
@@ -869,24 +875,24 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" s="5">
-        <f>0.2*J3</f>
-        <v>1370</v>
+        <f>0.12*J3</f>
+        <v>822</v>
       </c>
       <c r="E8" s="5">
-        <f t="shared" si="1"/>
-        <v>5480</v>
+        <f>+D8*C8</f>
+        <v>1644</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I8" t="s">
         <v>35</v>
@@ -899,21 +905,21 @@
         <v>7</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="5">
         <f>0.1*J3</f>
         <v>685</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="1"/>
-        <v>685</v>
+        <f>+D9*C9</f>
+        <v>1370</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>27</v>
@@ -929,400 +935,394 @@
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" s="5">
-        <f>0.13*J3</f>
-        <v>890.5</v>
+        <f>0.58*J3</f>
+        <v>3972.9999999999995</v>
       </c>
       <c r="E10" s="5">
-        <f t="shared" si="1"/>
-        <v>4452.5</v>
+        <f>+D10*C10</f>
+        <v>3972.9999999999995</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>29</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>21</v>
+      <c r="B11" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5">
-        <f>0.12*J3</f>
-        <v>822</v>
+        <f>0.18*J3</f>
+        <v>1233</v>
       </c>
       <c r="E11" s="5">
-        <f t="shared" si="1"/>
-        <v>1644</v>
+        <f>+D11*C11</f>
+        <v>1233</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>22</v>
+      <c r="B12" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5">
+        <f>0.61*J3</f>
+        <v>4178.5</v>
+      </c>
+      <c r="E12" s="5">
+        <f>+D12*C12</f>
+        <v>16714</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <f>0.22*J3</f>
+        <v>1507</v>
+      </c>
+      <c r="E13" s="5">
+        <f>+D13*C13</f>
+        <v>1507</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
         <f>0.1*J3</f>
         <v>685</v>
       </c>
-      <c r="E12" s="5">
-        <f t="shared" si="1"/>
+      <c r="E14" s="5">
+        <f t="shared" ref="E14" si="1">+D14*C14</f>
+        <v>685</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <f>0.53*J3</f>
+        <v>3630.5</v>
+      </c>
+      <c r="E15" s="5">
+        <f>+D15*C15</f>
+        <v>3630.5</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <f>0.36*J3</f>
+        <v>2466</v>
+      </c>
+      <c r="E16" s="5">
+        <f>+D16*C16</f>
+        <v>2466</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <f>0.31*J3</f>
+        <v>2123.5</v>
+      </c>
+      <c r="E17" s="5">
+        <f>+D17*C17</f>
+        <v>2123.5</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="I17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5">
+        <f>0.35*J3</f>
+        <v>2397.5</v>
+      </c>
+      <c r="E18" s="5">
+        <f>+D18*C18</f>
+        <v>2397.5</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5">
+        <f>0.2*J3</f>
         <v>1370</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="E19" s="5">
+        <f>+D19*C19</f>
+        <v>1370</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="5">
+        <f>0.22*J3</f>
+        <v>1507</v>
+      </c>
+      <c r="E20" s="5">
+        <f>+D20*C20</f>
+        <v>3014</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
+        <f>0.43*J3</f>
+        <v>2945.5</v>
+      </c>
+      <c r="E21" s="5">
+        <f>+D21*C21</f>
+        <v>2945.5</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
+        <f>6.23*J3</f>
+        <v>42675.5</v>
+      </c>
+      <c r="E22" s="5">
+        <f>+D22*C22</f>
+        <v>42675.5</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5">
+        <f>3.97*J3</f>
+        <v>27194.5</v>
+      </c>
+      <c r="E23" s="5">
+        <f>+D23*C23</f>
+        <v>54389</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5">
+        <f>25.99*J3</f>
+        <v>178031.5</v>
+      </c>
+      <c r="E24" s="5">
+        <f>+D24*C24</f>
+        <v>178031.5</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5">
         <f>4.02*J3</f>
         <v>27536.999999999996</v>
       </c>
-      <c r="E13" s="5">
-        <f t="shared" si="1"/>
+      <c r="E25" s="5">
+        <f>+D25*C25</f>
         <v>27536.999999999996</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F25" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="5">
-        <f>0.18*J3</f>
-        <v>1233</v>
-      </c>
-      <c r="E14" s="5">
-        <f t="shared" si="1"/>
-        <v>1233</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2">
-        <v>4</v>
-      </c>
-      <c r="D15" s="5">
-        <f>0.61*J3</f>
-        <v>4178.5</v>
-      </c>
-      <c r="E15" s="5">
-        <f t="shared" si="1"/>
-        <v>16714</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1</v>
-      </c>
-      <c r="D16" s="5">
-        <f>0.22*J3</f>
-        <v>1507</v>
-      </c>
-      <c r="E16" s="5">
-        <f t="shared" si="1"/>
-        <v>1507</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5">
-        <f>0.1*J3</f>
-        <v>685</v>
-      </c>
-      <c r="E17" s="5">
-        <f t="shared" ref="E17" si="2">+D17*C17</f>
-        <v>685</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5">
-        <f>0.53*J3</f>
-        <v>3630.5</v>
-      </c>
-      <c r="E18" s="5">
-        <f t="shared" si="1"/>
-        <v>3630.5</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5">
-        <f>0.36*J3</f>
-        <v>2466</v>
-      </c>
-      <c r="E19" s="5">
-        <f t="shared" si="1"/>
-        <v>2466</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
-        <f>0.31*J3</f>
-        <v>2123.5</v>
-      </c>
-      <c r="E20" s="5">
-        <f t="shared" si="1"/>
-        <v>2123.5</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
-        <f>0.35*J3</f>
-        <v>2397.5</v>
-      </c>
-      <c r="E21" s="5">
-        <f t="shared" si="1"/>
-        <v>2397.5</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-      <c r="D22" s="5">
-        <f>0.2*J3</f>
-        <v>1370</v>
-      </c>
-      <c r="E22" s="5">
-        <f t="shared" si="1"/>
-        <v>1370</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="5">
-        <f>0.22*J3</f>
-        <v>1507</v>
-      </c>
-      <c r="E23" s="5">
-        <f t="shared" si="1"/>
-        <v>3014</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5">
-        <f>0.43*J3</f>
-        <v>2945.5</v>
-      </c>
-      <c r="E24" s="5">
-        <f t="shared" si="1"/>
-        <v>2945.5</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="2">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5">
-        <f>0.58*J3</f>
-        <v>3972.9999999999995</v>
-      </c>
-      <c r="E25" s="5">
-        <f t="shared" si="1"/>
-        <v>3972.9999999999995</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="G25" s="7"/>
     </row>
@@ -1331,11 +1331,11 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="16"/>
+      <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="5"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E26:E29" si="2">+D26*C26</f>
         <v>0</v>
       </c>
       <c r="F26" s="2"/>
@@ -1346,11 +1346,11 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="16"/>
+      <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="5"/>
+      <c r="D27" s="2"/>
       <c r="E27" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F27" s="2"/>
@@ -1361,11 +1361,11 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="16"/>
+      <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-      <c r="D28" s="5"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F28" s="2"/>
@@ -1380,7 +1380,7 @@
       <c r="C29" s="2"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F29" s="2"/>
@@ -1395,7 +1395,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E29:E30" si="3">+D30*C30</f>
         <v>0</v>
       </c>
       <c r="F30" s="2"/>
@@ -1403,29 +1403,29 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" xr:uid="{15D952FA-8284-4B8B-BA52-5536EF27B64A}"/>
-    <hyperlink ref="F4" r:id="rId2" xr:uid="{AE7C954F-D8E6-4C87-A1DB-E8E761E03657}"/>
-    <hyperlink ref="F5" r:id="rId3" xr:uid="{997B98EB-1BE7-4E41-AE42-B3A348D55D49}"/>
-    <hyperlink ref="F6" r:id="rId4" xr:uid="{98E3D5B9-3CB9-40F7-BD21-A223CA98A252}"/>
-    <hyperlink ref="F7" r:id="rId5" xr:uid="{8D12C66E-62D7-42A4-A923-B2EE4DBAB3B0}"/>
-    <hyperlink ref="F8" r:id="rId6" xr:uid="{8E2EFE7E-9CC5-40C2-899D-505567008B6F}"/>
-    <hyperlink ref="F9" r:id="rId7" xr:uid="{23C3F479-2761-4355-B3B1-55A53D24E872}"/>
-    <hyperlink ref="F10" r:id="rId8" xr:uid="{AC42AEB2-3CB3-436B-AC84-9FCDBCC53652}"/>
-    <hyperlink ref="F11" r:id="rId9" xr:uid="{39CEC9E4-93D2-42DB-B3EF-A0DC8B1BF649}"/>
-    <hyperlink ref="F12" r:id="rId10" xr:uid="{DE7DC490-28C5-40D4-8096-A5D0B4E8CA34}"/>
-    <hyperlink ref="F13" r:id="rId11" xr:uid="{B7B8B7DD-9349-431A-B540-977095D47509}"/>
-    <hyperlink ref="F14" r:id="rId12" xr:uid="{32C9BBE2-B085-40ED-9482-C4A992B92774}"/>
-    <hyperlink ref="F15" r:id="rId13" xr:uid="{CB98356C-D2C9-46B4-9472-35C102687020}"/>
-    <hyperlink ref="F16" r:id="rId14" xr:uid="{0E83BAD7-E761-4479-827D-EFCD9C540B64}"/>
-    <hyperlink ref="F17" r:id="rId15" xr:uid="{5832DA8D-1D91-4BA2-A2D4-66ADE83D90AC}"/>
-    <hyperlink ref="F18" r:id="rId16" xr:uid="{771AA51C-6524-4515-B611-123D4125843F}"/>
-    <hyperlink ref="F19" r:id="rId17" xr:uid="{0E3B9535-05EC-41BD-AEA4-2A7FFEA4202F}"/>
-    <hyperlink ref="F20" r:id="rId18" xr:uid="{D7482E33-5741-4772-BE1F-1C86D70BBB69}"/>
-    <hyperlink ref="F21" r:id="rId19" xr:uid="{DCF11D56-D35C-4F46-928E-D4EEFCC2D5C3}"/>
-    <hyperlink ref="F22" r:id="rId20" xr:uid="{CCDC8CEA-D755-4010-A535-AC6796494C79}"/>
-    <hyperlink ref="F23" r:id="rId21" xr:uid="{0E642852-5587-4BB4-9B46-453C26D50C0A}"/>
-    <hyperlink ref="F24" r:id="rId22" xr:uid="{CFC35A0D-235D-4F0F-ACB1-2308605BCF6D}"/>
-    <hyperlink ref="F25" r:id="rId23" xr:uid="{6D01D0F5-F729-4C23-954F-F4F0335975FC}"/>
+    <hyperlink ref="F22" r:id="rId1" xr:uid="{15D952FA-8284-4B8B-BA52-5536EF27B64A}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{AE7C954F-D8E6-4C87-A1DB-E8E761E03657}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{997B98EB-1BE7-4E41-AE42-B3A348D55D49}"/>
+    <hyperlink ref="F24" r:id="rId4" xr:uid="{98E3D5B9-3CB9-40F7-BD21-A223CA98A252}"/>
+    <hyperlink ref="F23" r:id="rId5" xr:uid="{8D12C66E-62D7-42A4-A923-B2EE4DBAB3B0}"/>
+    <hyperlink ref="F5" r:id="rId6" xr:uid="{8E2EFE7E-9CC5-40C2-899D-505567008B6F}"/>
+    <hyperlink ref="F6" r:id="rId7" xr:uid="{23C3F479-2761-4355-B3B1-55A53D24E872}"/>
+    <hyperlink ref="F7" r:id="rId8" xr:uid="{AC42AEB2-3CB3-436B-AC84-9FCDBCC53652}"/>
+    <hyperlink ref="F8" r:id="rId9" xr:uid="{39CEC9E4-93D2-42DB-B3EF-A0DC8B1BF649}"/>
+    <hyperlink ref="F9" r:id="rId10" xr:uid="{DE7DC490-28C5-40D4-8096-A5D0B4E8CA34}"/>
+    <hyperlink ref="F25" r:id="rId11" xr:uid="{B7B8B7DD-9349-431A-B540-977095D47509}"/>
+    <hyperlink ref="F11" r:id="rId12" xr:uid="{32C9BBE2-B085-40ED-9482-C4A992B92774}"/>
+    <hyperlink ref="F12" r:id="rId13" xr:uid="{CB98356C-D2C9-46B4-9472-35C102687020}"/>
+    <hyperlink ref="F13" r:id="rId14" xr:uid="{0E83BAD7-E761-4479-827D-EFCD9C540B64}"/>
+    <hyperlink ref="F14" r:id="rId15" xr:uid="{5832DA8D-1D91-4BA2-A2D4-66ADE83D90AC}"/>
+    <hyperlink ref="F15" r:id="rId16" xr:uid="{771AA51C-6524-4515-B611-123D4125843F}"/>
+    <hyperlink ref="F16" r:id="rId17" xr:uid="{0E3B9535-05EC-41BD-AEA4-2A7FFEA4202F}"/>
+    <hyperlink ref="F17" r:id="rId18" xr:uid="{D7482E33-5741-4772-BE1F-1C86D70BBB69}"/>
+    <hyperlink ref="F18" r:id="rId19" xr:uid="{DCF11D56-D35C-4F46-928E-D4EEFCC2D5C3}"/>
+    <hyperlink ref="F19" r:id="rId20" xr:uid="{CCDC8CEA-D755-4010-A535-AC6796494C79}"/>
+    <hyperlink ref="F20" r:id="rId21" xr:uid="{0E642852-5587-4BB4-9B46-453C26D50C0A}"/>
+    <hyperlink ref="F21" r:id="rId22" xr:uid="{CFC35A0D-235D-4F0F-ACB1-2308605BCF6D}"/>
+    <hyperlink ref="F10" r:id="rId23" xr:uid="{6D01D0F5-F729-4C23-954F-F4F0335975FC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId24"/>

--- a/Hardware/mini-vehiculo-exploracion-pcb/Assets/componentes.xlsx
+++ b/Hardware/mini-vehiculo-exploracion-pcb/Assets/componentes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\STAY AWAY MUGGLE\FIUNA\mini-vehiculo-exploracion\Hardware\mini-vehiculo-exploracion-pcb\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EEF678-D41A-4861-BBF8-1AC39AB31E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604BB9BE-B898-4CD0-ADC1-6E4BB552E8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FD0E3963-897E-470D-880E-FBDA975F4A9A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="123">
   <si>
     <t>Ítem</t>
   </si>
@@ -232,6 +232,180 @@
   </si>
   <si>
     <t>Cristal 32.7680 kHz</t>
+  </si>
+  <si>
+    <t>UJ20-C-H-G-SMT-P16-TR</t>
+  </si>
+  <si>
+    <t>USBLC6-2SC6</t>
+  </si>
+  <si>
+    <t>C1Q 1</t>
+  </si>
+  <si>
+    <t>SD1206S040S1R0</t>
+  </si>
+  <si>
+    <t>Capacitor 22uF</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0iuGIwTO</t>
+  </si>
+  <si>
+    <t>Conector JST Hembra 8P</t>
+  </si>
+  <si>
+    <t>Resistencia 820 Ohm</t>
+  </si>
+  <si>
+    <t>Capacitor 47 nF</t>
+  </si>
+  <si>
+    <t>10% 6.3V</t>
+  </si>
+  <si>
+    <t>https://mou.sr/3FQNKzj</t>
+  </si>
+  <si>
+    <t>Capacitor 1uF 6.3V</t>
+  </si>
+  <si>
+    <t>Capacitor 1uF 16V</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4148sDz</t>
+  </si>
+  <si>
+    <t>5% 16V</t>
+  </si>
+  <si>
+    <t>Capacitor 0.1 uF 16V</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4smuSvr</t>
+  </si>
+  <si>
+    <t>5% 16VDC</t>
+  </si>
+  <si>
+    <t>Capacitor Elect. 180uF 16V</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4bywcEn</t>
+  </si>
+  <si>
+    <t>20% 16VDC</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4d167QN</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4lHNtzP</t>
+  </si>
+  <si>
+    <t>https://mou.sr/479RXcr</t>
+  </si>
+  <si>
+    <t>1% 100ppm 3/4W</t>
+  </si>
+  <si>
+    <t>0.5% 25ppm 1/8W</t>
+  </si>
+  <si>
+    <t>Esquema Eléctrico</t>
+  </si>
+  <si>
+    <t>https://mou.sr/40VUCTl</t>
+  </si>
+  <si>
+    <t>1.1A 15V</t>
+  </si>
+  <si>
+    <t>Fusible Resetable PPTC 1.1A</t>
+  </si>
+  <si>
+    <t>Fusible Reseteable PPTC 2A</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4dejjSk</t>
+  </si>
+  <si>
+    <t>2A 24V</t>
+  </si>
+  <si>
+    <t>https://mou.sr/3Z3jqrX</t>
+  </si>
+  <si>
+    <t>LDO 5V a 3.3V</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4rMTrAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulador de Voltaje </t>
+  </si>
+  <si>
+    <t>https://mou.sr/40C82ns</t>
+  </si>
+  <si>
+    <t>TPS561208DDCR</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4d0RoFw</t>
+  </si>
+  <si>
+    <t>MAX8891EXK33/V+T</t>
+  </si>
+  <si>
+    <t>TPS564257DRLR</t>
+  </si>
+  <si>
+    <t>MOSFET Canal P</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4szqtFy</t>
+  </si>
+  <si>
+    <t>https://mou.sr/3PjdRUA</t>
+  </si>
+  <si>
+    <t>https://mou.sr/4d1wZjF</t>
+  </si>
+  <si>
+    <t>Resistencia 221 kOhm</t>
+  </si>
+  <si>
+    <t>Resistencia 220 kOhm</t>
+  </si>
+  <si>
+    <t>Resistencia 30 kOhm</t>
+  </si>
+  <si>
+    <t>Resistencia 56.2 kOhm</t>
+  </si>
+  <si>
+    <t>Capacitor 100 nF</t>
+  </si>
+  <si>
+    <t>Capacitor 22 uF</t>
+  </si>
+  <si>
+    <t>Capacitor 10 uF</t>
+  </si>
+  <si>
+    <t>Capacitor 10 pF</t>
+  </si>
+  <si>
+    <t>Capacitor 47 uF</t>
+  </si>
+  <si>
+    <t>Bobina 4.7 uH</t>
+  </si>
+  <si>
+    <t>Servomotor SG90</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0dEFMOoa</t>
   </si>
 </sst>
 </file>
@@ -242,7 +416,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,8 +447,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,6 +499,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -347,7 +535,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -363,13 +551,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -686,14 +882,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5052AD-E57D-4C3D-BF60-E11D66D6B798}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="49.44140625" customWidth="1"/>
     <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -734,7 +930,7 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="18" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="2">
@@ -745,7 +941,7 @@
         <v>91790</v>
       </c>
       <c r="E3" s="5">
-        <f>+D3*C3</f>
+        <f t="shared" ref="E3:E13" si="0">+D3*C3</f>
         <v>91790</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -764,7 +960,7 @@
         <f>1+A3</f>
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2">
@@ -775,7 +971,7 @@
         <v>56649.5</v>
       </c>
       <c r="E4" s="5">
-        <f>+D4*C4</f>
+        <f t="shared" si="0"/>
         <v>56649.5</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -785,10 +981,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <f t="shared" ref="A5:A30" si="0">1+A4</f>
+        <f t="shared" ref="A5:A56" si="1">1+A4</f>
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="18" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="2">
@@ -799,7 +995,7 @@
         <v>1370</v>
       </c>
       <c r="E5" s="5">
-        <f>+D5*C5</f>
+        <f t="shared" si="0"/>
         <v>5480</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -811,10 +1007,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="18" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="2">
@@ -825,7 +1021,7 @@
         <v>685</v>
       </c>
       <c r="E6" s="5">
-        <f>+D6*C6</f>
+        <f t="shared" si="0"/>
         <v>685</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -834,17 +1030,17 @@
       <c r="G6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="21" t="s">
         <v>33</v>
       </c>
       <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="18" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="2">
@@ -855,7 +1051,7 @@
         <v>890.5</v>
       </c>
       <c r="E7" s="5">
-        <f>+D7*C7</f>
+        <f t="shared" si="0"/>
         <v>4452.5</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -864,17 +1060,17 @@
       <c r="G7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="21" t="s">
         <v>34</v>
       </c>
       <c r="J7" s="9"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="18" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="2">
@@ -885,7 +1081,7 @@
         <v>822</v>
       </c>
       <c r="E8" s="5">
-        <f>+D8*C8</f>
+        <f t="shared" si="0"/>
         <v>1644</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -894,17 +1090,17 @@
       <c r="G8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="21" t="s">
         <v>35</v>
       </c>
       <c r="J8" s="10"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="18" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="2">
@@ -915,7 +1111,7 @@
         <v>685</v>
       </c>
       <c r="E9" s="5">
-        <f>+D9*C9</f>
+        <f t="shared" si="0"/>
         <v>1370</v>
       </c>
       <c r="F9" s="4" t="s">
@@ -924,17 +1120,17 @@
       <c r="G9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="14"/>
+      <c r="J9" s="13"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="18" t="s">
         <v>64</v>
       </c>
       <c r="C10" s="2">
@@ -945,20 +1141,24 @@
         <v>3972.9999999999995</v>
       </c>
       <c r="E10" s="5">
-        <f>+D10*C10</f>
+        <f t="shared" si="0"/>
         <v>3972.9999999999995</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>63</v>
       </c>
       <c r="G10" s="7"/>
+      <c r="I10" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="J10" s="20"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="2">
@@ -969,7 +1169,7 @@
         <v>1233</v>
       </c>
       <c r="E11" s="5">
-        <f>+D11*C11</f>
+        <f t="shared" si="0"/>
         <v>1233</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -979,22 +1179,22 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="15" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5">
         <f>0.61*J3</f>
         <v>4178.5</v>
       </c>
       <c r="E12" s="5">
-        <f>+D12*C12</f>
-        <v>16714</v>
+        <f t="shared" si="0"/>
+        <v>8357</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>42</v>
@@ -1005,10 +1205,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="2">
@@ -1019,7 +1219,7 @@
         <v>1507</v>
       </c>
       <c r="E13" s="5">
-        <f>+D13*C13</f>
+        <f t="shared" si="0"/>
         <v>1507</v>
       </c>
       <c r="F13" s="4" t="s">
@@ -1031,22 +1231,22 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="15" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5">
         <f>0.1*J3</f>
         <v>685</v>
       </c>
       <c r="E14" s="5">
-        <f t="shared" ref="E14" si="1">+D14*C14</f>
-        <v>685</v>
+        <f t="shared" ref="E14" si="2">+D14*C14</f>
+        <v>1370</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>26</v>
@@ -1057,10 +1257,10 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C15" s="2">
@@ -1071,20 +1271,22 @@
         <v>3630.5</v>
       </c>
       <c r="E15" s="5">
-        <f>+D15*C15</f>
+        <f t="shared" ref="E15:E34" si="3">+D15*C15</f>
         <v>3630.5</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="7"/>
+      <c r="G15" s="7" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C16" s="2">
@@ -1095,20 +1297,22 @@
         <v>2466</v>
       </c>
       <c r="E16" s="5">
-        <f>+D16*C16</f>
+        <f t="shared" si="3"/>
         <v>2466</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G16" s="7"/>
+      <c r="G16" s="7" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="2">
@@ -1119,23 +1323,25 @@
         <v>2123.5</v>
       </c>
       <c r="E17" s="5">
-        <f>+D17*C17</f>
+        <f t="shared" si="3"/>
         <v>2123.5</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G17" s="7"/>
+      <c r="G17" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="I17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="15" t="s">
         <v>54</v>
       </c>
       <c r="C18" s="2">
@@ -1146,32 +1352,34 @@
         <v>2397.5</v>
       </c>
       <c r="E18" s="5">
-        <f>+D18*C18</f>
+        <f t="shared" si="3"/>
         <v>2397.5</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="7"/>
+      <c r="G18" s="7" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="15" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="5">
         <f>0.2*J3</f>
         <v>1370</v>
       </c>
       <c r="E19" s="5">
-        <f>+D19*C19</f>
-        <v>1370</v>
+        <f t="shared" si="3"/>
+        <v>4110</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>56</v>
@@ -1182,10 +1390,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="2">
@@ -1196,10 +1404,10 @@
         <v>1507</v>
       </c>
       <c r="E20" s="5">
-        <f>+D20*C20</f>
+        <f t="shared" si="3"/>
         <v>3014</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="14" t="s">
         <v>58</v>
       </c>
       <c r="G20" s="7" t="s">
@@ -1208,10 +1416,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C21" s="2">
@@ -1222,20 +1430,22 @@
         <v>2945.5</v>
       </c>
       <c r="E21" s="5">
-        <f>+D21*C21</f>
+        <f t="shared" si="3"/>
         <v>2945.5</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G21" s="7"/>
+      <c r="G21" s="7">
+        <v>82350120560</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="15" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2">
@@ -1246,7 +1456,7 @@
         <v>42675.5</v>
       </c>
       <c r="E22" s="5">
-        <f>+D22*C22</f>
+        <f t="shared" si="3"/>
         <v>42675.5</v>
       </c>
       <c r="F22" s="4" t="s">
@@ -1256,164 +1466,792 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B24" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="5">
         <f>3.97*J3</f>
         <v>27194.5</v>
       </c>
-      <c r="E23" s="5">
-        <f>+D23*C23</f>
+      <c r="E24" s="5">
+        <f t="shared" si="3"/>
         <v>54389</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B24" s="13" t="s">
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5">
+        <f>0.1*J3</f>
+        <v>685</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" si="3"/>
+        <v>1370</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4</v>
+      </c>
+      <c r="D26" s="5">
+        <f>0.14*J3</f>
+        <v>959.00000000000011</v>
+      </c>
+      <c r="E26" s="5">
+        <f t="shared" si="3"/>
+        <v>3836.0000000000005</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
+      <c r="D27" s="5">
+        <f>0.28*J3</f>
+        <v>1918.0000000000002</v>
+      </c>
+      <c r="E27" s="5">
+        <f t="shared" si="3"/>
+        <v>3836.0000000000005</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="2">
+        <v>2</v>
+      </c>
+      <c r="D28" s="5">
+        <f>0.15*J3</f>
+        <v>1027.5</v>
+      </c>
+      <c r="E28" s="5">
+        <f t="shared" si="3"/>
+        <v>2055</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5">
+        <f>0.11*J3</f>
+        <v>753.5</v>
+      </c>
+      <c r="E29" s="5">
+        <f t="shared" si="3"/>
+        <v>1507</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="2">
+        <v>4</v>
+      </c>
+      <c r="D30" s="5">
+        <f>0.28*J3</f>
+        <v>1918.0000000000002</v>
+      </c>
+      <c r="E30" s="5">
+        <f t="shared" si="3"/>
+        <v>7672.0000000000009</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2</v>
+      </c>
+      <c r="D31" s="5">
+        <f>0.64*J3</f>
+        <v>4384</v>
+      </c>
+      <c r="E31" s="5">
+        <f t="shared" si="3"/>
+        <v>8768</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2</v>
+      </c>
+      <c r="D32" s="5">
+        <f>2.4975*J3</f>
+        <v>17107.875</v>
+      </c>
+      <c r="E32" s="5">
+        <f t="shared" si="3"/>
+        <v>34215.75</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B33" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="2">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5">
         <f>25.99*J3</f>
         <v>178031.5</v>
       </c>
-      <c r="E24" s="5">
-        <f>+D24*C24</f>
+      <c r="E33" s="5">
+        <f t="shared" si="3"/>
         <v>178031.5</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B25" s="13" t="s">
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="2">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5">
         <f>4.02*J3</f>
         <v>27536.999999999996</v>
       </c>
-      <c r="E25" s="5">
-        <f>+D25*C25</f>
+      <c r="E34" s="5">
+        <f t="shared" si="3"/>
         <v>27536.999999999996</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="5">
-        <f t="shared" ref="E26:E29" si="2">+D26*C26</f>
+      <c r="G34" s="7"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5">
+        <f>1*J3</f>
+        <v>6850</v>
+      </c>
+      <c r="E35" s="5">
+        <f t="shared" ref="E35:E56" si="4">+D35*C35</f>
+        <v>6850</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2</v>
+      </c>
+      <c r="D36" s="5">
+        <f>0.42*J3</f>
+        <v>2877</v>
+      </c>
+      <c r="E36" s="5">
+        <f t="shared" si="4"/>
+        <v>5754</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="2">
+        <v>2</v>
+      </c>
+      <c r="D37" s="5">
+        <f>0.55*J3</f>
+        <v>3767.5000000000005</v>
+      </c>
+      <c r="E37" s="5">
+        <f t="shared" si="4"/>
+        <v>7535.0000000000009</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="2">
+        <v>4</v>
+      </c>
+      <c r="D38" s="5">
+        <f>0.9*J3</f>
+        <v>6165</v>
+      </c>
+      <c r="E38" s="5">
+        <f t="shared" si="4"/>
+        <v>24660</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G38" s="7"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="2">
+        <v>2</v>
+      </c>
+      <c r="D39" s="5">
+        <f>2.4*J3</f>
+        <v>16440</v>
+      </c>
+      <c r="E39" s="5">
+        <f t="shared" si="4"/>
+        <v>32880</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="2">
+        <v>2</v>
+      </c>
+      <c r="D40" s="5">
+        <f>0.52*J3</f>
+        <v>3562</v>
+      </c>
+      <c r="E40" s="5">
+        <f t="shared" si="4"/>
+        <v>7124</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="2">
+        <v>2</v>
+      </c>
+      <c r="D41" s="5">
+        <f>0.58*J3</f>
+        <v>3972.9999999999995</v>
+      </c>
+      <c r="E41" s="5">
+        <f t="shared" si="4"/>
+        <v>7945.9999999999991</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2</v>
+      </c>
+      <c r="D42" s="5">
+        <f>0.25*J3</f>
+        <v>1712.5</v>
+      </c>
+      <c r="E42" s="5">
+        <f t="shared" si="4"/>
+        <v>3425</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G42" s="7"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="2">
+        <v>2</v>
+      </c>
+      <c r="D43" s="5">
+        <f>0.83*J3</f>
+        <v>5685.5</v>
+      </c>
+      <c r="E43" s="5">
+        <f t="shared" si="4"/>
+        <v>11371</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G43" s="7"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="2">
+        <v>2</v>
+      </c>
+      <c r="D44" s="5">
+        <f>1.51*J3</f>
+        <v>10343.5</v>
+      </c>
+      <c r="E44" s="5">
+        <f t="shared" si="4"/>
+        <v>20687</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G44" s="7"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="2">
+        <v>4</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="5">
-        <f t="shared" si="2"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="5">
-        <f t="shared" si="2"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="7"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5">
-        <f t="shared" si="2"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="7"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B48" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" s="2">
+        <v>2</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5">
-        <f t="shared" ref="E29:E30" si="3">+D30*C30</f>
+      <c r="F48" s="4"/>
+      <c r="G48" s="7"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="7"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="7"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="2">
+        <v>4</v>
+      </c>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="7"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51" s="2">
+        <v>3</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="7"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="7"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="7"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="7"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="7"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="2">
+        <v>2</v>
+      </c>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F22" r:id="rId1" xr:uid="{15D952FA-8284-4B8B-BA52-5536EF27B64A}"/>
     <hyperlink ref="F3" r:id="rId2" xr:uid="{AE7C954F-D8E6-4C87-A1DB-E8E761E03657}"/>
     <hyperlink ref="F4" r:id="rId3" xr:uid="{997B98EB-1BE7-4E41-AE42-B3A348D55D49}"/>
-    <hyperlink ref="F24" r:id="rId4" xr:uid="{98E3D5B9-3CB9-40F7-BD21-A223CA98A252}"/>
-    <hyperlink ref="F23" r:id="rId5" xr:uid="{8D12C66E-62D7-42A4-A923-B2EE4DBAB3B0}"/>
+    <hyperlink ref="F33" r:id="rId4" xr:uid="{98E3D5B9-3CB9-40F7-BD21-A223CA98A252}"/>
+    <hyperlink ref="F24" r:id="rId5" xr:uid="{8D12C66E-62D7-42A4-A923-B2EE4DBAB3B0}"/>
     <hyperlink ref="F5" r:id="rId6" xr:uid="{8E2EFE7E-9CC5-40C2-899D-505567008B6F}"/>
     <hyperlink ref="F6" r:id="rId7" xr:uid="{23C3F479-2761-4355-B3B1-55A53D24E872}"/>
     <hyperlink ref="F7" r:id="rId8" xr:uid="{AC42AEB2-3CB3-436B-AC84-9FCDBCC53652}"/>
     <hyperlink ref="F8" r:id="rId9" xr:uid="{39CEC9E4-93D2-42DB-B3EF-A0DC8B1BF649}"/>
     <hyperlink ref="F9" r:id="rId10" xr:uid="{DE7DC490-28C5-40D4-8096-A5D0B4E8CA34}"/>
-    <hyperlink ref="F25" r:id="rId11" xr:uid="{B7B8B7DD-9349-431A-B540-977095D47509}"/>
+    <hyperlink ref="F34" r:id="rId11" xr:uid="{B7B8B7DD-9349-431A-B540-977095D47509}"/>
     <hyperlink ref="F11" r:id="rId12" xr:uid="{32C9BBE2-B085-40ED-9482-C4A992B92774}"/>
     <hyperlink ref="F12" r:id="rId13" xr:uid="{CB98356C-D2C9-46B4-9472-35C102687020}"/>
     <hyperlink ref="F13" r:id="rId14" xr:uid="{0E83BAD7-E761-4479-827D-EFCD9C540B64}"/>
@@ -1426,8 +2264,23 @@
     <hyperlink ref="F20" r:id="rId21" xr:uid="{0E642852-5587-4BB4-9B46-453C26D50C0A}"/>
     <hyperlink ref="F21" r:id="rId22" xr:uid="{CFC35A0D-235D-4F0F-ACB1-2308605BCF6D}"/>
     <hyperlink ref="F10" r:id="rId23" xr:uid="{6D01D0F5-F729-4C23-954F-F4F0335975FC}"/>
+    <hyperlink ref="F35" r:id="rId24" xr:uid="{29965E5F-A992-4866-B525-74C84367D255}"/>
+    <hyperlink ref="F28" r:id="rId25" xr:uid="{2B1CD5B2-6349-4663-B9A7-2629DFC8A12D}"/>
+    <hyperlink ref="F29" r:id="rId26" xr:uid="{0A19DC31-EEEE-4E84-AFC3-A1A944DA3737}"/>
+    <hyperlink ref="F30" r:id="rId27" xr:uid="{7A0F2DD0-90D3-4425-827A-3385D18878C2}"/>
+    <hyperlink ref="F31" r:id="rId28" xr:uid="{FE2D2B9D-0CFD-4E41-9F3E-AB2DE3D1F514}"/>
+    <hyperlink ref="F25" r:id="rId29" xr:uid="{DD3E0974-8402-46C1-A65A-F7DAD72E01D6}"/>
+    <hyperlink ref="F36" r:id="rId30" xr:uid="{9495CFE3-070F-4476-898A-DAF43A39CA33}"/>
+    <hyperlink ref="F37" r:id="rId31" xr:uid="{F5216815-27C7-46E4-9720-BD54AAF87450}"/>
+    <hyperlink ref="F39" r:id="rId32" xr:uid="{E1BC2A3B-02A9-478F-9E30-E80545768D30}"/>
+    <hyperlink ref="F40" r:id="rId33" xr:uid="{7273A71B-912E-4158-A9AF-07C0D9D1F7EC}"/>
+    <hyperlink ref="F41" r:id="rId34" xr:uid="{5C56623F-8EB3-44FA-936E-F59B1AAE1C58}"/>
+    <hyperlink ref="F42" r:id="rId35" xr:uid="{7347ADD7-52E9-4526-BC70-66582A3979C4}"/>
+    <hyperlink ref="F43" r:id="rId36" xr:uid="{3603C8A3-4753-42C4-99CA-087570D0CF3C}"/>
+    <hyperlink ref="F44" r:id="rId37" xr:uid="{D7D80267-A051-453C-83EA-F7CF4B012714}"/>
+    <hyperlink ref="F32" r:id="rId38" xr:uid="{5AB973BB-96FA-411D-90A9-B71947A7FA5A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId24"/>
+  <pageSetup orientation="portrait" r:id="rId39"/>
 </worksheet>
 </file>